--- a/artfynd/A 59455-2025 artfynd.xlsx
+++ b/artfynd/A 59455-2025 artfynd.xlsx
@@ -5111,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG41" t="b">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
@@ -6362,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="AE52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG52" t="b">
         <v>0</v>
@@ -6695,7 +6695,7 @@
         <v>0</v>
       </c>
       <c r="AE55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG55" t="b">
         <v>0</v>
